--- a/Starlink_Pool_AddOns.xlsx
+++ b/Starlink_Pool_AddOns.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthony/Desktop/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Desktop\SMARTCAST-LABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8542762D-6A53-EB40-B5FA-F5161C844419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8658BEF-B6B0-4BC5-B003-DE72C13F5952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="1755" windowWidth="21600" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOns" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Description</t>
   </si>
@@ -464,7 +469,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -472,7 +477,7 @@
     <col min="4" max="4" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -498,296 +503,302 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3" s="4">
+        <v>46259</v>
+      </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="4"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4"/>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="4"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="4"/>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="4"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="4"/>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="4"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="4"/>
       <c r="D39" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>16</v>
       </c>

--- a/Starlink_Pool_AddOns.xlsx
+++ b/Starlink_Pool_AddOns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Desktop\SMARTCAST-LABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8658BEF-B6B0-4BC5-B003-DE72C13F5952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4600EE28-7517-421B-9CB1-C4AE776DFD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4725" yWindow="1755" windowWidth="21600" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Description</t>
   </si>
@@ -516,9 +516,15 @@
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46261</v>
+      </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">

--- a/Starlink_Pool_AddOns.xlsx
+++ b/Starlink_Pool_AddOns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Desktop\SMARTCAST-LABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4600EE28-7517-421B-9CB1-C4AE776DFD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB388E0-FE7C-4D0C-88C7-B3643147DBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4725" yWindow="1755" windowWidth="21600" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Description</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Tab must stay named "AddOns" and the header names must not change - the dashboard matches on them.</t>
+  </si>
+  <si>
+    <t>2 TB add on</t>
   </si>
 </sst>
 </file>
@@ -528,9 +531,15 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C5" s="4">
+        <v>46262</v>
+      </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
